--- a/spring_02/result.xlsx
+++ b/spring_02/result.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="209">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -493,6 +493,80 @@
 Text-vision hybrid attention</t>
   </si>
   <si>
+    <t xml:space="preserve">text and images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonic Polyp segmentation: split to 8-1-1
+CVC-ClinicDB, CVC-ColonDB, 
+ETIS-LaribPolypDB, Kvasir, PolypGen
+MRI brain tumor segmentation:
+LGG Segmentation Dataset from Cancer Imaging Archive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Mean Intersection Over Union (mIoU)
+-Mean Dice Coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on the polyp dataset: 
++1.38% in mDice and +3.36% in mIoU
+on the brain tumor dataset: 
++4.1% in mDice and +3.94% in mIoU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimTxtSeg: two components
+-Textual-to-Visual Cue Converter that produces visual prompts 
+from text prompts on medical images and bouning boxes 
+And use them to generate pseudo masks with SAM
+-text-guided segmentation model with 
+Text-Vision Hybrid Attention that fuses text and image features
+(train it using the final generated psuedo masks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-use mmdetection framework to fine-tune 
+Textual-to-Visual Cue Converter based on Swin-T
+-2 text prompts granularities for each task:
+Individual words and descriptive sentences
+And use GPT-4 to generate concise sentences with 20 words
+-pre-train Textual to Visual Cue Convertor with:
+Adam optimizer with learning rate init = 2*10e-4
+Weight decay = 1*10e-4
+Batch size = 8
+Epochs = 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Textual-to-Visual Cue Converter: consists of 
+image and text backbones, feature enhancer,
+feature fusion, language guided query selection, cross modality decoder
+-Text-Guided Segmentation with Text-Vision Hybrid Attention:
+Vision Encoder &amp; Text Encoder: ConvNext- Tiny as vision encoder
+Text-Vision Hybrid Attention Decoder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations: 
+-performance of the framework is heavily dependent on 
+the version of the Segment Anything Model (SAM) used
+-the study has not yet been extended to other complex medical imaging areas
+(3D scans or different types like skin lesions, chest X-rays)
+-TVCC requires initial domain-specific pre-training on a dataset 
+with bounding boxes (ODVG format) before it can be applied to new datasets
+Notes: 
+-the same text is used for all images form the same class
+-TVHA is more complex with Self-Attention, Text-to-Vision, Vision-to-Text 
+and then followed by a Channel Attention module
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all datasets are public
+But no url was mentionned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PolypGen dataset:
+https://www.synapse.org/Synapse:syn26376615/wiki/613312
+LGG Segmentation Dataset: mentionned from the Cancer Imaging Archive:
+But the repo github mentionned the Brain tumor segmentation dataset:
+https://www.kaggle.com/datasets/nikhilroxtomar/brain-tumor-segmentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://github.com/xyx1024/SimTxtSeg</t>
   </si>
   <si>
@@ -515,6 +589,90 @@
 Vision-language models
 Foundation models
 Weakly supervised segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image and text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all the previous dataset
+With 
+Breast Ultrasound (UDIAT): 
+50-113 validate-test instead of 65-98 validate-test
+Brain MRI: 
+1,002-600 validate-test instead of 400-400 validate-test
++
+Chest CT segmentation:
+(7,959-3,010-1,800)
+For train-validate-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-segmentation rerformance metrics:
+DSC, normalized surface distance (NSD)
+-cross-modal retrieval metrics/
+top-1 and top-2 accuracy
+-uncertainty and statistical metrics:
+entropy, p-value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+13.07% in Dice score for zero-shot 
+and +11.21% in Dice score weakly supervised </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MedCLIP-SAMv2:
+enhanced framework that builds on MedCLIP-SAM by by refining CLIP-SAM integration, 
+Saliency-guided prompt generation, and uncertainty-aware weak supervision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Efficient DHN-NCE Fine-Tuning: 
+fine-tune the BiomedCLIP model using DHN-NCE Loss, 
+decoupling, base encoders 
+(ViT for images and PubMedBERT for text)
+2-Zero-Shot Medical Image Segmentation: 
+generates segmentation masks using 
+LLM Prompt Generation (GPT-4)
+M2IB Saliency Maps, initial segmentation, SAM Refinement
+3-Uncertainty-Aware Weakly Supervised Segmentation: 
+Use pseudo-masks as weak labels to train specialized segmentation 
+network from scratch by integrating 
+NnUNet architecture, checkpoint ensembling,
+uncertainty estimation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Propose new CLIP training/fine-tuning loss function (DHN-NCE)
+-Introduce a text-driven zero-shot medical segmentation method 
+combining CLIP and SAM for radiological tasks
+-Explore a weakly-supervised strategy for further refine
+zero-shot segmentation results with uncertainty estimation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-the framework is limited to 2D binary segmentation tasks 
+because of the 2D architecture of the BiomedCLIP encoder
+so tt can’t directly handle 3D volumetric data
+-no multi-class segmentation
+-using too many LLM prompts can introduce redundancy or noise
+Notes:
+-LLM-generated descriptive prompts (GPT-4) consistently 
+outperformed manually crafted keywords across most tasks
+-the framework is compatible with any interactive segmentation 
+foundation model (ScribblePrompt or SegVol)
+-uncertainty estimation (entropy maps) allow clinicians 
+to identify specific regions where the AI is less confident
+-the proposed DHN-NCE loss is noted for its efficiency 
+allowing for high performance even with small batch sizes
+Future work: 
+-extend the framework to 3D medical data 
+-expand validation to histopathology and surgical video 
+-explore multi-class segmentation strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the previous datasets 
++
+MedPix dataset:
+https://drive.google.com/file/d/1GrTyC08-CwP90TKO2aoMOj0tTyNiafjd/view?pli=1
++
+Chest CT Segmentation:
+https://www.kaggle.com/datasets/polomarco/chest-ct-segmentation</t>
   </si>
   <si>
     <t xml:space="preserve">https://github.com/HealthX-Lab/MedCLIP-SAMv2</t>
@@ -966,7 +1124,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1029,18 +1187,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1096,7 +1242,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1141,6 +1287,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1153,6 +1303,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1161,11 +1315,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1177,10 +1331,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1193,24 +1343,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1218,10 +1360,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1732,250 +1870,291 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="true" ht="185" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+    <row r="4" customFormat="false" ht="185" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="T4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="U4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="V4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="X4" s="8"/>
-      <c r="XFC4" s="13"/>
+      <c r="X4" s="4"/>
     </row>
-    <row r="5" s="18" customFormat="true" ht="138.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="n">
+    <row r="5" s="13" customFormat="true" ht="219.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="11" t="n">
         <v>45453</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14" t="s">
+      <c r="L5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="T5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14" t="s">
+      <c r="U5" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="X5" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="XFC5" s="19"/>
+      <c r="X5" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="XFC5" s="14"/>
     </row>
-    <row r="6" customFormat="false" ht="233.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+    <row r="6" s="13" customFormat="true" ht="321.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="20" t="n">
+      <c r="F6" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="15" t="n">
         <v>45785</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4" t="s">
+      <c r="I6" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4" t="s">
+      <c r="U6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="X6" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="V6" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="XFC6" s="14"/>
     </row>
-    <row r="7" customFormat="false" ht="100.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+    <row r="7" s="20" customFormat="true" ht="100.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="B7" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4" t="s">
+      <c r="F7" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="XFC7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>108</v>
+      <c r="B8" s="22" t="s">
+        <v>127</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>110</v>
+        <v>128</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>25</v>
@@ -1983,37 +2162,38 @@
       <c r="F8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G8" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="23" t="n">
+      <c r="G8" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" s="24" t="n">
         <v>45253</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>114</v>
+        <v>131</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>133</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="V8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="121.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>115</v>
+      <c r="B9" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>117</v>
+        <v>135</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>12</v>
@@ -2021,37 +2201,38 @@
       <c r="F9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="H9" s="23" t="n">
+      <c r="G9" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="24" t="n">
         <v>45681</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>120</v>
+        <v>138</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>139</v>
       </c>
       <c r="T9" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="V9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>121</v>
+      <c r="B10" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>123</v>
+        <v>141</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>1</v>
@@ -2059,37 +2240,38 @@
       <c r="F10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="23" t="n">
+      <c r="G10" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" s="24" t="n">
         <v>45905</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>145</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="V10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="76.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>127</v>
+      <c r="B11" s="22" t="s">
+        <v>146</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>129</v>
+        <v>147</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>148</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>1</v>
@@ -2098,19 +2280,19 @@
         <v>14</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="23" t="n">
+        <v>149</v>
+      </c>
+      <c r="H11" s="24" t="n">
         <v>45967</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>132</v>
+      <c r="J11" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>151</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>41</v>
@@ -2120,14 +2302,14 @@
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>133</v>
+      <c r="B12" s="22" t="s">
+        <v>152</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>135</v>
+        <v>153</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0</v>
@@ -2136,19 +2318,19 @@
         <v>12</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="H12" s="24" t="n">
         <v>45975</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>139</v>
+        <v>156</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>158</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>41</v>
@@ -2158,14 +2340,14 @@
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>140</v>
+      <c r="B13" s="22" t="s">
+        <v>159</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0</v>
@@ -2174,36 +2356,36 @@
         <v>20</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="23" t="n">
+        <v>162</v>
+      </c>
+      <c r="H13" s="24" t="n">
         <v>45980</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>145</v>
+        <v>163</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>164</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>147</v>
+      <c r="B14" s="22" t="s">
+        <v>166</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>53</v>
@@ -2212,19 +2394,19 @@
         <v>10</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="H14" s="23" t="n">
+        <v>169</v>
+      </c>
+      <c r="H14" s="24" t="n">
         <v>44584</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>152</v>
+        <v>170</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>41</v>
@@ -2234,14 +2416,14 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="25" t="s">
-        <v>153</v>
+      <c r="B15" s="22" t="s">
+        <v>172</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>155</v>
+        <v>173</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>174</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -2250,19 +2432,19 @@
         <v>15</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="23" t="n">
+        <v>175</v>
+      </c>
+      <c r="H15" s="24" t="n">
         <v>45998</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>158</v>
+        <v>105</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>177</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>41</v>
@@ -2272,14 +2454,14 @@
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>159</v>
+      <c r="B16" s="22" t="s">
+        <v>178</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -2288,19 +2470,19 @@
         <v>20</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="H16" s="23" t="n">
+        <v>181</v>
+      </c>
+      <c r="H16" s="24" t="n">
         <v>46058</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>163</v>
+      <c r="I16" s="22" t="s">
+        <v>182</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="K16" s="21" t="s">
-        <v>165</v>
+        <v>183</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>184</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>41</v>
@@ -2310,14 +2492,14 @@
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>166</v>
+      <c r="B17" s="22" t="s">
+        <v>185</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>168</v>
+        <v>186</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>187</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>652</v>
@@ -2326,16 +2508,16 @@
         <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>170</v>
+        <v>188</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>189</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>41</v>
@@ -2345,59 +2527,59 @@
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>172</v>
+      <c r="B18" s="22" t="s">
+        <v>191</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>174</v>
+        <v>192</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>193</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="H18" s="23" t="n">
+      <c r="F18" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="24" t="n">
         <v>45920</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="K18" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="M18" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="O18" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q18" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="R18" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="S18" s="21" t="s">
-        <v>187</v>
+        <v>197</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="N18" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="P18" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q18" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="R18" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="S18" s="22" t="s">
+        <v>206</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>62</v>
@@ -2405,14 +2587,14 @@
       <c r="U18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V18" s="21" t="s">
-        <v>188</v>
+      <c r="V18" s="22" t="s">
+        <v>207</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2421,19 +2603,20 @@
     <hyperlink ref="G3" r:id="rId2" display="https://doi.org/10.1007/978-3-031-72390-2_60"/>
     <hyperlink ref="G4" r:id="rId3" display="https://arxiv.org/abs/2405.14230"/>
     <hyperlink ref="G5" r:id="rId4" display="https://doi.org/10.1007/978-3-031-72111-3_60"/>
-    <hyperlink ref="X6" r:id="rId5" display="https://github.com/HealthX-Lab/MedCLIP-SAMv2"/>
-    <hyperlink ref="G7" r:id="rId6" display="https://ieeexplore.ieee.org/document/9669626"/>
-    <hyperlink ref="G8" r:id="rId7" display="https://doi.org/10.1016/j.compbiomed.2023.107744"/>
-    <hyperlink ref="G9" r:id="rId8" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
-    <hyperlink ref="G10" r:id="rId9" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
-    <hyperlink ref="G11" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
-    <hyperlink ref="G12" r:id="rId11" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
-    <hyperlink ref="G13" r:id="rId12" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
-    <hyperlink ref="G14" r:id="rId13" display="https://doi.org/10.1016/j.media.2022.102374"/>
-    <hyperlink ref="G15" r:id="rId14" display="https://doi.org/10.1016/j.media.2025.103894"/>
-    <hyperlink ref="G16" r:id="rId15" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
-    <hyperlink ref="G17" r:id="rId16" display="https://arxiv.org/abs/2303.00915"/>
-    <hyperlink ref="X18" r:id="rId17" display="https://github.com/MrGiovanni/R-Super"/>
+    <hyperlink ref="V5" r:id="rId5" display="https://www.synapse.org/Synapse:syn26376615/wiki/613312"/>
+    <hyperlink ref="X6" r:id="rId6" display="https://github.com/HealthX-Lab/MedCLIP-SAMv2"/>
+    <hyperlink ref="G7" r:id="rId7" display="https://ieeexplore.ieee.org/document/9669626"/>
+    <hyperlink ref="G8" r:id="rId8" display="https://doi.org/10.1016/j.compbiomed.2023.107744"/>
+    <hyperlink ref="G9" r:id="rId9" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
+    <hyperlink ref="G11" r:id="rId11" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
+    <hyperlink ref="G12" r:id="rId12" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
+    <hyperlink ref="G13" r:id="rId13" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
+    <hyperlink ref="G14" r:id="rId14" display="https://doi.org/10.1016/j.media.2022.102374"/>
+    <hyperlink ref="G15" r:id="rId15" display="https://doi.org/10.1016/j.media.2025.103894"/>
+    <hyperlink ref="G16" r:id="rId16" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
+    <hyperlink ref="G17" r:id="rId17" display="https://arxiv.org/abs/2303.00915"/>
+    <hyperlink ref="X18" r:id="rId18" display="https://github.com/MrGiovanni/R-Super"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/spring_02/result.xlsx
+++ b/spring_02/result.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="218">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -750,6 +750,84 @@
 Cross-domain medical image generation</t>
   </si>
   <si>
+    <t xml:space="preserve">-used images and masks
+for segmentation task
+-need only the image 
+and the 
+generated difference map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTS 2020
+TCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification task:
+Accuracy
+Recall
+F1 score
+AUC (area under the ROC curve)
+Segmentation task:
+Sensitivity
+Dice similarity coefficient (Dice)
+Mean intersection over union (mIoU) 
+95% Hausdorff Distance (HD95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDA-GAN is better than the best SOTA baseline 
+In classification task in terms of 
+0.50%, 1.72%, 2.05%, 0.21% 
+ACC, AUC, Recall, F1
+In Segmentation task in terms of
+2.50%, 0.90%, 14.96%, 4.18% 
+Dice, Sens, HD95, mIOU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attention-guided cross-domain tumor image generation model (CDA-GAN):
+to resolve the lack of inter-class difference information problem,
+incorporate channel attention into a CycleGAN-based 
+Cross-domain generation network  that captures inter domain information 
+and generates positive or negative samples of brain tumors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-use CDA-GAN to generate positive samples
+(with lesions) and negative samples (without lesions)
+-Attention-guided Adversarial Loss
+-Pixel-level Attention Loss: used to reduce 
+the difference between ROI and generated attentio map
+-Cycle-consistency Loss: 
+used to enforce forward and backward consistency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on advanced CycleGAN, they added:
+-AMSE (Average-Max Squeeze-and-Excitation) Block: 
+performs channel-wise feature recalibration 
+to improve the model's representational ability, 
+capture the differences between domains and correctly translate them
+-Semi-supervised Spatial Attention-Guided Generator: 
+the model is forced to focus on the specific ROI
+rather than just general image features
+-Attention-Guided Discriminator with Spectral Normalization: 
+forces the discriminator to pay more attention to 
+the changing parts of the image (the lesions) 
+While stabilizing the training process to prevent mode collapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-it’s based entirely on 2D slices
+-using newer Diffusion-based models (like DDPM) performed poorly on the datasets. 
+Notes:
+-CDA-GAN has higher training cost compared to other models like CycleGAN or UAGGAN 
+due to the additional modules (AMSE blocks and semi-supervised attention)
+-the authors noted that the stability of attention modules can be highly susceptible 
+to very small or extremely imbalanced datasets
+-the semi-supervised mask guidance is specifically used for the positive-to-negative translation
+and the negative-to-positive process is performed without mask supervision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brain MRI Segmentation:
+https://www.kaggle.com/datasets/mateuszbuda/lgg-mri-segmentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enhanced brain tumor detection and segmentation using densely 
 Connected convolutional networks with stacking ensemble learning </t>
   </si>
@@ -1124,7 +1202,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1175,12 +1253,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1242,7 +1314,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1275,6 +1347,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1283,11 +1363,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1295,15 +1395,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1311,22 +1419,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1335,7 +1427,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1343,23 +1435,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1942,297 +2030,329 @@
       </c>
       <c r="X4" s="4"/>
     </row>
-    <row r="5" s="13" customFormat="true" ht="219.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+    <row r="5" customFormat="false" ht="219.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="8" t="n">
         <v>45453</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="Q5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="R5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="T5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="W5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="X5" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="XFC5" s="14"/>
     </row>
-    <row r="6" s="13" customFormat="true" ht="321.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+    <row r="6" customFormat="false" ht="321.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="9" t="n">
         <v>45785</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="R6" s="9" t="s">
+      <c r="R6" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="T6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="9" t="s">
+      <c r="V6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="W6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="X6" s="8" t="s">
+      <c r="X6" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="XFC6" s="14"/>
     </row>
-    <row r="7" s="20" customFormat="true" ht="100.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+    <row r="7" s="14" customFormat="true" ht="114.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16" t="s">
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="16"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="XFC7" s="21"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="XFC7" s="15"/>
     </row>
-    <row r="8" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" s="14" customFormat="true" ht="214.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="18" t="n">
         <v>45253</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="L8" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="R8" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="V8" s="25"/>
+      <c r="U8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="XFC8" s="15"/>
     </row>
-    <row r="9" customFormat="false" ht="121.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+    <row r="9" s="20" customFormat="true" ht="121.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="B9" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="24" t="n">
+      <c r="G9" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="23" t="n">
         <v>45681</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="J9" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="T9" s="1" t="s">
+      <c r="J9" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="T9" s="20" t="s">
         <v>41</v>
       </c>
       <c r="V9" s="25"/>
+      <c r="XFC9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>140</v>
+      <c r="B10" s="27" t="s">
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>142</v>
+        <v>150</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>151</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>1</v>
@@ -2240,38 +2360,38 @@
       <c r="F10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="H10" s="24" t="n">
+      <c r="G10" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>45905</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J10" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>145</v>
+      <c r="J10" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="T10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V10" s="25"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="76.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>146</v>
+      <c r="B11" s="27" t="s">
+        <v>155</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>148</v>
+        <v>156</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>157</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>1</v>
@@ -2279,20 +2399,20 @@
       <c r="F11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="G11" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" s="24" t="n">
+      <c r="G11" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <v>45967</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>151</v>
+      <c r="J11" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>41</v>
@@ -2302,14 +2422,14 @@
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>152</v>
+      <c r="B12" s="27" t="s">
+        <v>161</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>154</v>
+        <v>162</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0</v>
@@ -2317,20 +2437,20 @@
       <c r="F12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G12" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" s="24" t="n">
+      <c r="G12" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="29" t="n">
         <v>45975</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>158</v>
+        <v>165</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>167</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>41</v>
@@ -2340,14 +2460,14 @@
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>159</v>
+      <c r="B13" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0</v>
@@ -2355,37 +2475,37 @@
       <c r="F13" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="H13" s="24" t="n">
+      <c r="G13" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="29" t="n">
         <v>45980</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J13" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>173</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>166</v>
+      <c r="B14" s="27" t="s">
+        <v>175</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>53</v>
@@ -2393,20 +2513,20 @@
       <c r="F14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="24" t="n">
+      <c r="G14" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="29" t="n">
         <v>44584</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>105</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>171</v>
+        <v>179</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>180</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>41</v>
@@ -2416,14 +2536,14 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>172</v>
+      <c r="B15" s="27" t="s">
+        <v>181</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>174</v>
+        <v>182</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>183</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -2431,20 +2551,20 @@
       <c r="F15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="H15" s="24" t="n">
+      <c r="G15" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="29" t="n">
         <v>45998</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>177</v>
+      <c r="J15" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>186</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>41</v>
@@ -2454,14 +2574,14 @@
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>178</v>
+      <c r="B16" s="27" t="s">
+        <v>187</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -2469,20 +2589,20 @@
       <c r="F16" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G16" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="H16" s="24" t="n">
+      <c r="G16" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="H16" s="29" t="n">
         <v>46058</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>184</v>
+      <c r="I16" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>193</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>41</v>
@@ -2492,14 +2612,14 @@
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>185</v>
+      <c r="B17" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>187</v>
+        <v>195</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>652</v>
@@ -2508,16 +2628,16 @@
         <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>189</v>
+        <v>197</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>198</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>41</v>
@@ -2527,59 +2647,59 @@
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>191</v>
+      <c r="B18" s="27" t="s">
+        <v>200</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>193</v>
+        <v>201</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>202</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="H18" s="24" t="n">
+      <c r="F18" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="H18" s="29" t="n">
         <v>45920</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="N18" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="P18" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q18" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="R18" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="S18" s="22" t="s">
+      <c r="J18" s="31" t="s">
         <v>206</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="M18" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="O18" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="P18" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q18" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="R18" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="S18" s="27" t="s">
+        <v>215</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>62</v>
@@ -2587,14 +2707,14 @@
       <c r="U18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V18" s="22" t="s">
-        <v>207</v>
+      <c r="V18" s="27" t="s">
+        <v>216</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2603,20 +2723,21 @@
     <hyperlink ref="G3" r:id="rId2" display="https://doi.org/10.1007/978-3-031-72390-2_60"/>
     <hyperlink ref="G4" r:id="rId3" display="https://arxiv.org/abs/2405.14230"/>
     <hyperlink ref="G5" r:id="rId4" display="https://doi.org/10.1007/978-3-031-72111-3_60"/>
-    <hyperlink ref="V5" r:id="rId5" display="https://www.synapse.org/Synapse:syn26376615/wiki/613312"/>
+    <hyperlink ref="V5" r:id="rId5" display="PolypGen dataset:&#10;https://www.synapse.org/Synapse:syn26376615/wiki/613312&#10;&#10;LGG Segmentation Dataset: mentionned from the Cancer Imaging Archive:&#10;But the repo github mentionned the Brain tumor segmentation dataset:&#10;https://www.kaggle.com/datasets/nikhilroxtomar/brain-tumor-segmentation"/>
     <hyperlink ref="X6" r:id="rId6" display="https://github.com/HealthX-Lab/MedCLIP-SAMv2"/>
     <hyperlink ref="G7" r:id="rId7" display="https://ieeexplore.ieee.org/document/9669626"/>
     <hyperlink ref="G8" r:id="rId8" display="https://doi.org/10.1016/j.compbiomed.2023.107744"/>
-    <hyperlink ref="G9" r:id="rId9" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
-    <hyperlink ref="G10" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
-    <hyperlink ref="G11" r:id="rId11" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
-    <hyperlink ref="G12" r:id="rId12" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
-    <hyperlink ref="G13" r:id="rId13" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
-    <hyperlink ref="G14" r:id="rId14" display="https://doi.org/10.1016/j.media.2022.102374"/>
-    <hyperlink ref="G15" r:id="rId15" display="https://doi.org/10.1016/j.media.2025.103894"/>
-    <hyperlink ref="G16" r:id="rId16" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
-    <hyperlink ref="G17" r:id="rId17" display="https://arxiv.org/abs/2303.00915"/>
-    <hyperlink ref="X18" r:id="rId18" display="https://github.com/MrGiovanni/R-Super"/>
+    <hyperlink ref="V8" r:id="rId9" display="https://www.kaggle.com/datasets/mateuszbuda/lgg-mri-segmentation"/>
+    <hyperlink ref="G9" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
+    <hyperlink ref="G10" r:id="rId11" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
+    <hyperlink ref="G11" r:id="rId12" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
+    <hyperlink ref="G12" r:id="rId13" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
+    <hyperlink ref="G13" r:id="rId14" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
+    <hyperlink ref="G14" r:id="rId15" display="https://doi.org/10.1016/j.media.2022.102374"/>
+    <hyperlink ref="G15" r:id="rId16" display="https://doi.org/10.1016/j.media.2025.103894"/>
+    <hyperlink ref="G16" r:id="rId17" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
+    <hyperlink ref="G17" r:id="rId18" display="https://arxiv.org/abs/2303.00915"/>
+    <hyperlink ref="X18" r:id="rId19" display="https://github.com/MrGiovanni/R-Super"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/spring_02/result.xlsx
+++ b/spring_02/result.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="264">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -858,6 +858,126 @@
 VGG-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Labls for classification 
+Masks for segmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dataset-I: 7023 samples and 4 classes (80-20 train-test)
+Dataset-II: 3264 samples and 4 classes
+Dataset-III: BraTS2020 (369-125) (train-validate)
+Dataset-IV: BraTS2021 (1251)
+Dataset-V: BraTS2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification metrics: 
+Accuracy, Sensitivity (Recall), Precision, 
+F1-score, Specificity,
+ Matthews Correlation Coefficient (MCC), AUC
+Segmentation metrics: 
+Dice Coefficient, Dice Loss, 
+Binary Cross Entropy Dice Loss,
+Hausdorff Distance at 95% (HD95)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy: 99.65 % (Dataset-I)
+Sensitivity (Recall): 98.97%  (Dataset-I)
+Precision: 99.76%  (Dataset-I)
+F1-score: 99.0%  (Dataset-III)
+Specificity: 100%  (Dataset-I)
+MCC: 99.87%  (Dataset-I)
+AUC: 1.00  (Dataset-I and  Dataset-IV)
+Dice Coefficient: 97.43%  (Dataset-I)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SEL-DenseNet201:
+-involves designing a stacked DenseNet201 as the meta- model called SEL-DenseNet201
+-it’s divided into two distinct levels:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">level-0 (base models):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">complemented by 6 diverse base models 
+(MobileNet-v3, 3D-CNN, VGG-16, VGG-19, ResNet50, AlexNet) </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">-3 loss functions: 
+Categorical cross-entropy, dice loss, binary cross entropy dice loss
+-regularization (dropout layers and weight decay)
+adam optimizer (learning rate = 0.0001)
+epochs = 25 
+batch size = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-level-0: base-level models (weak learners)
+6 pre-trained CNNs to capture various features and aspects of the MRI scans:
+-level-1: meta-model (the stacked layer)
+use DenseNet201 as the meta-learner
+it was chosen as the meta-model because its dense connections 
+allow each layer to receive inputs from all preceding layers 
+to facilitate better information flow, reuse feature maps, 
+help mitigate the vanishing gradient problem more effectively
+the model further enhances feature representation 
+By incorporating Squeeze-and-Excitation blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-the model was trained and evaluated on only 
+one specific brain tumor MRI dataset for its core development
+-researchers only utilized DenseNet201 as the meta-model at level-1,
+they didn’t test other models
+Notes:
+-SEL-DenseNet201 took over 58 minutes to train on Dataset-IV 
+and ~ 61 minutes on Dataset-V
+-traditional CNNs often struggle with gradients 
+becoming too small during backpropagation, 
+-VGG-16 and VGG-19 have high parameter counts
+(this increases memory usage and the risk of overfitting)
+-3D-CNN requires significant computational resources 
+and memory due to 3D convolution operations
+Future work:
+-test MobileNet-v3, ResNet50, AlexNet separately as meta-models to compare results
+-implement advanced loss function techniques
+-researchers intend to develop hybrid models that combine 
+deep learning feature extraction 
+with traditional machine learning classifiers
+-utilizing MRI datasets from other sources such as BraTS2018 and BraTS2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dataset-I: Brain tumor MRI dataset:
+https://www.kaggle.com/datasets/masoudnickparvar/brain-tumor-mri-dataset/data
+Dataset-II: Brain tumor classification (MRI):
+https://www.kaggle.com/datasets/sartajbhuvaji/brain-tumor-classification-mri
+Dataset-III: BraTS2020
+Dataset-IV: BraTS2021
+Dataset-V: BraTS2023
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medical SAM-Clip Grafting for brain tumor segmentation</t>
   </si>
   <si>
@@ -885,6 +1005,119 @@
 Deep learning</t>
   </si>
   <si>
+    <t xml:space="preserve">pixel level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTS2023: 1251 annotated brain tumor samples
+70-10-20 for train-validate-test
+-use BraTS 2018 dataset as an additional benchmark 
+to evaluate and test model’s performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Dice Score 
+-95% Hausdorff Distance (HD95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-on BraTS2023:
+Dice Score: 87.39±0.24%
+HD95: 5.68±0.05 mm
+-on BraTS2018:
+Dice Score: 87.19±0.21%
+HD95: 4.84±0.05 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the medical SAM-CLIP grafting network (MSCG):
+-combine the precise geometric localization of the Segment Anything Model (SAM) 
+with the rich semantic context of CLIP (Contrastive Language–Image Pre-training) 
+-it consists of 3 primary components:
+1-dual encoder: 2 parallel encoders to extract different types of info:
+SAM Image Encoder (SAM-Med3D) and CLIP Image Encoder (CT-CLIP)
+2-SC-Grafting module
+3-fusion decoder: generates the final segmentation masks 
+by integrating the features processed by the dual encoder, it’s organized into 3 flows:
+semantic flow, detail flow, seg mamba decoder
+Epochs = 200 
+batch size = 2 
+SGD with initial learning rate = 0.01
+Cosine annealing scheduler for learning rate decay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-dual encoder: 
+-SAM image encoder (SAM-Med3D): 
+focuses on learning global contextual representations and structural details, 
+it processes all four modalities concatenated together 
+to understand the overall shape and structure of the tumor
+-CLIP image encoder (CT-CLIP): 
+structure-oriented to extracte fine-grained semantic features from each modality 
+independently, it provides the medical domain knowledge that the original SAM lacks
+2-SC-Grafting module: 
+facilitate feature alignment between the SAM and CLIP branches,
+it grafts semantic info from the CLIP feature space 
+into the SAM model at multiple layers  (specifically 3, 6, 9, 12 layers)
+it uses scale grafting operation to unify 
+the different resolutions of the two encoders
+3-fusion decoder: generate the final segmentation masks 
+by integrating the features processed by the dual encoder, its flows are:
+a-semantic flow: reshape and upsample 
+the patch-wise features from the encoders into 3D shapes
+b-detail flow: uses 3D convolutional layers 
+to extract high-resolution details directly from the raw input images
+c-seg mamba decoder: employs 3D Mamba blocks 
+which provide a global receptive field with linear computational complexity
+4-frozen encoders to leverage the massive pre-training of the foundation models
+5-use 4 loss functions: dice loss, BCE loss, IoU loss, focal tversky loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-foundation model grafting: 
+authors graft rich semantic info from the CLIP (Contrastive Language–Image Pre-training)
+ feature space into the SAM model which allows the model to benefit from 
+SAM's geometric precision and CLIP's high-level semantic context simultaneously
+-dual encoding strategy: 
+use SAM branch: (concatenates all modalities to learn global contextual 
+representations and overall tumor shapes) and CLIP branch
+(orocesses each modality independently to extract 
+fine-grained modality-specific structural details)
+-multi-level feature alignment: 
+SC-grafting module aligns features at multiple specific layers 
+to ensure that both low-level spatial details and high-level abstract 
+meanings are integrated throughout the encoding process
+-efficient 3D decoding via mamba: 
+to provide a global receptive field (similar to transformers) 
+but with linear computational complexity
+-frozen weights strategy: 
+train only the SC-grafting modules and the fusion decoder,
+this prevents the model from losing its general segmentation 
+capabilities due to the relatively small size of medical datasets
+-composite multi-task loss: 
+training is guided by a combination of 
+4 distinct loss functions (Dice, BCE, IoU, and Focal Tversky)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-use only one dataset
+-the original SAM was trained primarily on natural images 
+which means it lacks medical-specific knowledge out of the box
+-SAM requires manually offered prompts 
+(bounding boxes or points) to generate results
+Notes:
+-use all the 4 MRI modalities (T1, T1-Gd, T2, FLAIR) 
+-SAM branch uses a shared patch embedding layer for each of the four modalities 
+before merging them with a linear layer while the CLIP branch uses 4 separately 
+randomly initialized patch embedding layers for the modalities, this difference 
+allows the CLIP branch to be more structure-oriented, 
+extracting independent features from each modality, 
+while the SAM branch focuses on holistic contextual information
+-experiments were conducted on an Intel Core i7 processor 
+paired with an NVIDIA 4090D GPU
+-authors found that fine-tuning large models like SAM and CLIP 
+on small medical datasets (like BraTS) led to poorer outcomes and performance degradation, 
+so they recommend freezing the weights of the large foundation models 
+and only training the grafting modules and the decoder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset is public</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diffusion-based knowledge distillation for effective multi-organ segmentation with reduced computational time</t>
   </si>
   <si>
@@ -910,6 +1143,118 @@
 Multi-organ</t>
   </si>
   <si>
+    <t xml:space="preserve">voxel-level </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTS2017, 2018, 2019
+for primary evaluation
+BraTS2020, 2021 
+to assess the model's generalizability
+RAOS (Rethinking Abdominal Organ Segmentation):
+413 CT scans and 3717 MRI scans
+divided into:
+Set A (cases without surgery): 
+220-97 samples for training-validation ~ 70/30
+Set B and C (post-surgical cases): 
+Used for testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dice Score
+Accuracy 
+Precision
+Sensitivity
+Specificity
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-on BraTS:
+student model: avg dice scores 
+94.27% (BraTS2017), 93.77% (BraTS2018), 93.80% (BraTS2019)
+peak dice score 95.6% on flair images
+-RAOS Dataset:
+Set A (no surgery): 
+student model gets acc 99.5%
+Set B (post-surgery, no missing organs): 
+99.8% acc and 95.82% dice score
+Set C (post-surgery, missing organs): 
+99.9% acc for the bladder and 95.56% dice for the spleen
+-time reduction: 2–3× reduction in computational time
+-model size: student model containes only 21M params 
+compared to the teacher (64M) 
+And other SOTA models (SwinUNETR 138M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3DKD-DiffuseNet
+3D Knowledge Distillation-based Diffusion Network:
+-designed for efficient and accurate 3D medical image segmentation
+-follows a teacher-student arch to achieve 
+high performance with lower computational costs
+-consists of 2 primary components:
+1-teacher model: 
+high-capacity 3D attention-based encoder-decoder 
+(3D Attention U-Net),
+uses 4-depth contraction-expansion path with max-pooling 
+2-student model: 
+lighter variant of the teacher, featuring 2-depth arch with fewer layers and filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique hybrid approach combining 
+traditional knowledge distillation with diffusion-based regularization:
+-knowledge distillation (KD): 
+the student model is supervised by both the original ground truth 
+and the teacher's soft-label outputs,
+this transfer is achieved by minimizing the Kullback–Leibler (KL) divergence 
+between the teacher and student's output distributions
+-diffusion-based regularization: 
+Repurposes diffusion as a regularizer during training
+-forward diffusion: add gaussian noise to the input images 
+-reverse diffusion: the student’s encoder acts as a denoising function 
+To reconstruct the clean image from the noisy input </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-diffusion consistency loss: 
+novel loss function that enforces spatial fidelity 
+and encourages the student to learn stable, 
+spatially coherent representations,
+the total loss is a weighted combination of cross-entropy, 
+distillation loss, this diffusion consistency loss
+-strategic preprocessing: 
+to further reduce computational time, 
+the model uses organ-specific intensity thresholding 
+and Region of Interest (ROI) identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-the model was trained and evaluated exclusively 
+On public benchmark datasets (BraTS and RAOS)
+-the model performance is lower on smaller or anatomically variable structures
+(the adrenal glands, gallbladder, femurs)
+(dice scores for the gallbladder is only 59-82%)
+-smaller organs have fewer voxels which reduces their influence 
+on the loss function during the training process and 
+make them harder for the model to learn accurately
+-the model faced increased complexity in the RAOS dataset (Sets B and C) 
+due to missing organs or altered anatomy resulting from surgery
+Notes:
+-batch size is only 2 during training due to 
+high computational cost of processing large 3D volumes
+-the model gains robustness from diffusion during training without suffering 
+the slow inference speeds typically associated with generative diffusion models
+Future work:
+-integrating real-time clinical datasets and diverse patient demographics
+-eExpanding the framework to include pediatric datasets
+-incorporating uncertainty-guided refinement 
+and 3D organ-specific shape priors to better delineate 
+challenging boundaries and small structures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTS are public
+RAOS: ask authors
++
+They provided this url but it doesn’t work
+ https://github.com/Luoxd1996/RAOS </t>
+  </si>
+  <si>
     <t xml:space="preserve">Enhancing zero-shot brain tumor subtype classification via fine-grained patch-text alignment </t>
   </si>
   <si>
@@ -936,6 +1281,112 @@
 Zero-shot classiﬁcation
 Whole slide image
 Vision-language model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patch level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training dataset:
+-CAMELYON: 500 whole slide images (WSIs) of sentinel lymph 
+node tissue sections from this repository
+Testing Datasets (Zero-Shot): 
+-EBRAINS (The Digital Tumor Atlas): 1,200 WSIs covering 
+30 fine-grained brain tumor subtypes
+-IPD-Brain: 484 WSIs corresponding to three glioma 
+subtypes (Glioblastoma, Astrocytoma, and Oligodendroglioma)
+-TCGA (The Cancer Genome Atlas): 429 WSIs used for 
+binary classification task between 
+Glioblastoma and Low-Grade Glioma
+-BRACS: 547 WSIs for breast carcinoma subtyping 
+(Benign, Atypical, and Malignant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Balanced accuracy
+-F1 Score
+-AUROC 
+(Area Under the Receiver Operating Characteristic curve)
+-Calibrated Text Prototype Dispersion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-EBRAINS30 (30 fine-grained subtypes): 
+balanced acc from 0.493 to 0.572 
+and F1 score from 0.542 to 0.597
+-EBRAINS12 (12 coarse-grained categories): 
+balanced acc of 0.712 and F1 score of 0.737
+-TCGA (Binary Classification):
+balanced accuracy 0.797 and F1 score 0.801
+-IPD-Brain (Glioma Subtypes):
+balanced acc 0.522 and AUROC of 0.833
+-BRACS (Breast Carcinoma):
+F1 score 0.334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine-Grained Patch Alignment Network (FG-PAN):
+-novel zero-shot framework specifically designed for the classification 
+of brain tumor subtypes from histopathological whole slide images (WSIs)
+-it’s built around a plug-and-play strategy that enhances existing 
+vision-language models without requiring retraining 
+or fine-tuning of the core parameters
+-it follows two primary flows: 
+1-visual flow: local feature refinement, it processes the raw WSI 
+to extract and refine visual features: patch selection module, 
+local window attention (LWA), gated feature fusion (GFF)
+2-textual flow: fine-grained description generation
+instead of using simple category names ("a photo of glioblastoma"), 
+this flow generates rich semantic context with LLM-guided prototypes and pathological specificity
+3-alignment and final prediction:
+patch-wise cross-modal classification and coordinate-aware aggregation
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-visual flow: processes the raw WSI to extract and refine visual features:
+-patch selection module: since WSIs are too large to process entirely, this training-free module 
+filters out non-informative background and selects a subset of representative patches, 
+it uses scores based on foreground ratio, morphological saliency (sharpness/texture), 
+semantic relevance to identify diagnostic regions
+-local window attention (LWA): to better capture spatial relationships, 
+the model divides patches into local windows and applies self-attention 
+within these windows to capture fine-grained patterns, 
+such as nuclear atypia which are often missed by global attention mechanisms
+-gated feature fusion (GFF): integrates the multi-head outputs from the LWA, 
+it uses a dynamic gating mechanism to selectively amplify diagnostically 
+salient features while suppressing noisy or redundant signals
+2-textual flow: 
+-LLM-guided prototypes: framework leverages LLMs (DeepSeek-R1) 
+to generate structured, pathology-aware descriptions for each tumor subtype
+-pathological specificity: these descriptions explicitly include molecular profiles 
+and histological signatures (microcystic honeycomb architecture)
+which helps the model differentiate between morphologically similar subtypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final prediction:
+-patch-wise cross-modal classification: 
+the refined visual patch features are aligned with the LLM-generated 
+textual prototypes in a shared embedding space using cosine similarity 
+-coordinate-aware aggregation: 
+to reach a final slide-level diagnosis, 
+the framework uses a weighting mechanism that considers both 
+the semantic confidence of each patch and its spatial location within the WSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-framework's effectiveness is influenced by the quality of 
+the LLM-generated descriptions  and the specific pathology 
+Foundation model (Conch or UNI) used for initial feature extraction
+-computational costs associated with high-resolution feature extraction 
+and generating complex prompts could potentially hinder 
+large-scale deployment in some environments
+Notes:
+-to ensure a rigorous evaluation, the model was trained on the CAMELYON dataset 
+(sentinel lymph node tissue) and tested on entirely different disease categories 
+(brain and breast tumors) that were never seen during training
+-key advantage of the FG-PAN modules (LWA, GFF, and FTDG) is that 
+they are plug-and-play means they can enhance existing vision-language models 
+without requiring retraining or fine-tuning of the core foundation model parameters
+-all experiments and benchmarks were performed using a single NVIDIA RTX4090 GPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask authors</t>
   </si>
   <si>
     <t xml:space="preserve">A comprehensive review of transformer models in brain tumor analysis </t>
@@ -961,7 +1412,135 @@
 Deep Learning</t>
   </si>
   <si>
+    <t xml:space="preserve">Voxel-level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-BraTS (Brain Tumor Segmentation Challenges): 
+provides multimodal MRI (T1, T1ce, T2, FLAIR) 
+with expert voxel-level annotations
+-TCGA (The Cancer Genome Atlas): 
+used for prognosis and biomarker prediction, 
+linking MRI scans with genomic data
+-Figshare Brain Tumor Dataset: 
+collection of 2D slices used mostly for classification
+-BR35H &amp; Masoud MRI Datasets: 
+adopted for developing lightweight 
+classification models and rapid prototyping
+-ADNI &amp; OASIS-3: 
+large neuroimaging cohorts 
+used for transfer learning and testing model 
+generalizability across broader clinical applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-segmentation metrics:
+Dice Similarity Coefficient (DSC)
+-classification and detection metrics:
+accuracy, precision, recall, 
+F1-score, area under the curve (AUC)
+-prognosis and prediction metrics:
+AUC for binary predictions, 
+Mean Absolute Error (MAE) or
+R² for regression-based prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-segmentation results:
+-Swin Transformer + UNet: dice score 0.94 on the BraTS 2015–2021
+-HHM-ZUNet: dice score of 98.43% + overall acc of 99.5%
+-P-PS3DCNN-GTOA: acc 99.9%
+-EA-DFFTU-Net: dice scores 95.6% (WT), 96.5% (TC), 92.6% (ET)
+-Hybrid 3DUNET (SSL + TL): 
+95.25% (WT), 89.56% (TC), 85.64% (ET) on BraTS 2021
+-classification and detection resulys:
+-Swin Transformer with ResMLP: classification acc 99.92% 
+-ensemble CNN (Bouguerra et al.): 100% acc on the Br35H 
+-OLiST (Optimized Lite Swin Transformer): 98.88% acc in detection
+-swin transformer models: 
+general detection accuracies up to 99.81%
+-explainable ViT: acc 98.75% for stroke detection 
+with high clinical transparency via Grad-CAM
+-prognosis and prediction results:
+ViT-WSI: 0.960 for IDH1, 0.874 for p53, 0.845 for MGMT
+RU-Net2+: prediction accuracies 85.71% for long-term, 
+72.72% for medium-term, 61.54% for short-term survival
+OViTAD: F1-scores 97.0% (rs-fMRI), 
+99.55% (sMRI) for predicting stages of Alzheimer's disease
+STAN: MAE of 4.124 years, R² of 0.933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-It’s a comprehensive systematic review of 124 peer-reviewed studies
+-they did identify 3 primary groups
+-Pure Transformer Models: rely solely on self-attention mechanisms 
+for feature representation (TransBTS, UNesT, MedFormer)
+-Hybrid Transformer Models: combine CNNs with Transformer backbones 
+to exploit both local spatial details and global contextual features 
+(BTSC-TNAS, DAUNet, Swin Transformer + UNet)
+-Specialized Transformer Models: incorporate domain-specific adaptations 
+to enhance performance in medical imaging, 
+such as handling missing MRI modalities or voxel-level clustering 
+(MM-UNet, MCTSeg, Supervoxel Transformer)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Self-Attention Mechanisms: 
+unlike CNNs which are biased toward local feature extraction, 
+Transformers use self-attention to capture 
+long-range spatial dependencies and global context
+-Cross-Attention Fusion: 
+rapidly evolving method where CNN and Transformer layers 
+exchange features iteratively to integrate local microstructures with global reasoning
+-Explainable AI (XAI): 
+the integration of tools like Grad-CAM, SHAP, LIME 
+to make black-box Transformer decisions transparent for clinical use
+-Multimodal Integration: 
+methods to fuse different MRI sequences 
+(T1, T2, FLAIR, T1ce) or combine imaging 
+with genomic data (radiogenomics) for prognosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-dataset limitations:
+-BraTS focus almost exclusively on gliomas and 
+utilize relatively homogeneous scanner protocols
+-high-quality voxel-level annotations are costly and time-consuming
+-collections like Figshare and BR35H provide only slice-level labels
+-technical and computational challenges:
+-the quadratic self-attention mechanism in Transformers 
+requires substantial memory and processing power which make these models 
+difficult to deploy in real-time clinical workflows or resource-constrained settings
+-transformer models require complex hyperparameter tuning compared to traditional CNNs
+-advanced cross-attention hybrid models often suffer 
+from elevated computational costs and training instability
+Notes:
+-growing shift toward models that can perform segmentation, 
+Classification, prognosis simultaneously
+-move toward hybrid CNN-Transformer architectures which attempt 
+to balance local spatial detail with global reasoning
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-BraTS 2017/18:
+med.upenn.edu/sbia/brats2017(or 2018)/data.html
+-BraTS 2019:
+med.upenn.edu/cbica/brats2019/data.html
+-BraTS 2020:
+med.upenn.edu/cbica/brats2020/data.html
+-BraTS 2021:
+kaggle.com/datasets/dschettler8845/brats-2021-task1
+-Figshare:
+kaggle.com/datasets/ashkhagan/figshare-brain-tumor-dataset
+-BR35H:
+kaggle.com/datasets/ahmedhamada0/brain-tumor-detection
+-Masoud:
+kaggle.com/datasets/masoudnickparvar/brain-tumor-mri-dataset
+-TCGA:
+cancer.gov/about-nci/organization/ccg/research/structural-genomics/tcga
+-OASIS3:
+sites.wustl.edu/oasisbrains/home/oasis-3/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">github.com/rkushol/ADDFormer</t>
   </si>
   <si>
     <t xml:space="preserve">Weakly supervised segmentation with cross-modality equivariant constraints</t>
@@ -983,6 +1562,9 @@
 Multi-modal segmentation
 Self-training
 Equivariant constraints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image level</t>
   </si>
   <si>
     <t xml:space="preserve">Diagnostic text-guided representation learning in hierarchical classification for pathological whole slide image</t>
@@ -1202,7 +1784,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1259,6 +1841,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1314,7 +1902,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1355,43 +1943,63 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1403,8 +2011,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1415,8 +2023,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1424,18 +2036,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1444,10 +2044,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1718,12 +2314,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="32.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="44.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="51.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="51.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="56.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="80.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="55.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="69.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="83.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="72.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="74.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="31.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="25"/>
@@ -2178,334 +2774,498 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="true" ht="114.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+    <row r="7" customFormat="false" ht="114.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10" t="s">
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="XFC7" s="15"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
     </row>
-    <row r="8" s="14" customFormat="true" ht="214.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="n">
+    <row r="8" customFormat="false" ht="214.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="13" t="n">
         <v>45253</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="O8" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="P8" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="Q8" s="16" t="s">
+      <c r="Q8" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="R8" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="S8" s="19" t="s">
+      <c r="S8" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="U8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="11" t="s">
+      <c r="V8" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="XFC8" s="15"/>
     </row>
-    <row r="9" s="20" customFormat="true" ht="121.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+    <row r="9" s="15" customFormat="true" ht="346.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="18" t="n">
         <v>45681</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="L9" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="T9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="V9" s="25"/>
-      <c r="XFC9" s="26"/>
+      <c r="U9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="W9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="XFC9" s="21"/>
     </row>
-    <row r="10" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" s="15" customFormat="true" ht="370.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="B10" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="H10" s="29" t="n">
+      <c r="G10" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="18" t="n">
         <v>45905</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="J10" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="T10" s="1" t="s">
+      <c r="J10" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="T10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="V10" s="4"/>
+      <c r="U10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="V10" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="W10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="XFC10" s="21"/>
     </row>
-    <row r="11" customFormat="false" ht="76.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" s="15" customFormat="true" ht="368.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="B11" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="G11" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="H11" s="29" t="n">
+      <c r="G11" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="18" t="n">
         <v>45967</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="T11" s="1" t="s">
+      <c r="J11" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="R11" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="S11" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="T11" s="15" t="s">
         <v>41</v>
       </c>
+      <c r="U11" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="W11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="XFC11" s="21"/>
     </row>
-    <row r="12" customFormat="false" ht="76.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" s="15" customFormat="true" ht="380.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="B12" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="G12" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="H12" s="29" t="n">
+      <c r="G12" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <v>45975</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J12" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="T12" s="1" t="s">
+      <c r="I12" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="R12" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="S12" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="T12" s="15" t="s">
         <v>41</v>
       </c>
+      <c r="U12" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="V12" s="24"/>
+      <c r="W12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="XFC12" s="21"/>
     </row>
-    <row r="13" customFormat="false" ht="91.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+    <row r="13" s="25" customFormat="true" ht="364.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="B13" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="29" t="n">
+      <c r="G13" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="H13" s="28" t="n">
         <v>45980</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>174</v>
-      </c>
+      <c r="I13" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="M13" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="N13" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="O13" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="P13" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q13" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="R13" s="31"/>
+      <c r="S13" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="T13" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="U13" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="V13" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="W13" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="XFC13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>175</v>
+      <c r="B14" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>53</v>
@@ -2513,20 +3273,23 @@
       <c r="F14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="29" t="n">
+      <c r="G14" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="H14" s="13" t="n">
         <v>44584</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>105</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>180</v>
+        <v>224</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>41</v>
@@ -2536,14 +3299,14 @@
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>181</v>
+      <c r="B15" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>183</v>
+        <v>228</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -2551,20 +3314,23 @@
       <c r="F15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="29" t="n">
+      <c r="G15" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>45998</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>186</v>
+      <c r="J15" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>41</v>
@@ -2574,14 +3340,14 @@
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>187</v>
+      <c r="B16" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -2589,20 +3355,23 @@
       <c r="F16" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G16" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="H16" s="29" t="n">
+      <c r="G16" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="H16" s="13" t="n">
         <v>46058</v>
       </c>
-      <c r="I16" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>193</v>
+      <c r="I16" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>41</v>
@@ -2612,14 +3381,14 @@
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>194</v>
+      <c r="B17" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>196</v>
+        <v>241</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>242</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>652</v>
@@ -2628,16 +3397,16 @@
         <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>198</v>
+        <v>243</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>244</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>41</v>
@@ -2647,59 +3416,59 @@
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>200</v>
+      <c r="B18" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>202</v>
+        <v>247</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>248</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="H18" s="29" t="n">
+      <c r="F18" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>45920</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="L18" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="M18" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="O18" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="P18" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q18" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="R18" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="S18" s="27" t="s">
-        <v>215</v>
+        <v>251</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>261</v>
       </c>
       <c r="T18" s="1" t="s">
         <v>62</v>
@@ -2707,14 +3476,14 @@
       <c r="U18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V18" s="27" t="s">
-        <v>216</v>
+      <c r="V18" s="11" t="s">
+        <v>262</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>42</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -2727,17 +3496,18 @@
     <hyperlink ref="X6" r:id="rId6" display="https://github.com/HealthX-Lab/MedCLIP-SAMv2"/>
     <hyperlink ref="G7" r:id="rId7" display="https://ieeexplore.ieee.org/document/9669626"/>
     <hyperlink ref="G8" r:id="rId8" display="https://doi.org/10.1016/j.compbiomed.2023.107744"/>
-    <hyperlink ref="V8" r:id="rId9" display="https://www.kaggle.com/datasets/mateuszbuda/lgg-mri-segmentation"/>
+    <hyperlink ref="V8" r:id="rId9" display="Brain MRI Segmentation:&#10;https://www.kaggle.com/datasets/mateuszbuda/lgg-mri-segmentation"/>
     <hyperlink ref="G9" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
     <hyperlink ref="G10" r:id="rId11" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
     <hyperlink ref="G11" r:id="rId12" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
-    <hyperlink ref="G12" r:id="rId13" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
-    <hyperlink ref="G13" r:id="rId14" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
-    <hyperlink ref="G14" r:id="rId15" display="https://doi.org/10.1016/j.media.2022.102374"/>
-    <hyperlink ref="G15" r:id="rId16" display="https://doi.org/10.1016/j.media.2025.103894"/>
-    <hyperlink ref="G16" r:id="rId17" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
-    <hyperlink ref="G17" r:id="rId18" display="https://arxiv.org/abs/2303.00915"/>
-    <hyperlink ref="X18" r:id="rId19" display="https://github.com/MrGiovanni/R-Super"/>
+    <hyperlink ref="V11" r:id="rId13" display="https://github.com/Luoxd1996/RAOS"/>
+    <hyperlink ref="G12" r:id="rId14" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
+    <hyperlink ref="G13" r:id="rId15" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
+    <hyperlink ref="G14" r:id="rId16" display="https://doi.org/10.1016/j.media.2022.102374"/>
+    <hyperlink ref="G15" r:id="rId17" display="https://doi.org/10.1016/j.media.2025.103894"/>
+    <hyperlink ref="G16" r:id="rId18" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
+    <hyperlink ref="G17" r:id="rId19" display="https://arxiv.org/abs/2303.00915"/>
+    <hyperlink ref="X18" r:id="rId20" display="https://github.com/MrGiovanni/R-Super"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/spring_02/result.xlsx
+++ b/spring_02/result.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="282">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -890,39 +890,11 @@
 Dice Coefficient: 97.43%  (Dataset-I)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SEL-DenseNet201:
+    <t xml:space="preserve">SEL-DenseNet201:
 -involves designing a stacked DenseNet201 as the meta- model called SEL-DenseNet201
 -it’s divided into two distinct levels:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">level-0 (base models):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">complemented by 6 diverse base models 
+level-0 (base models):complemented by 6 diverse base models 
 (MobileNet-v3, 3D-CNN, VGG-16, VGG-19, ResNet50, AlexNet) </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">-3 loss functions: 
@@ -1567,6 +1539,140 @@
     <t xml:space="preserve">image level</t>
   </si>
   <si>
+    <t xml:space="preserve">BraTS
+Prostate DECATHLON Segmentation Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dice Similarity Coefficient (DSC)
+Average Symmetric Surface Distance (ASSD)
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-On BraTS Dataset:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">improvements ranging from 6% (in T1 and T1c modalities) 
+to 12% in terms of DSC for the FLAIR modality
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-On Prostate DECATHLON Dataset:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">margin of 15% in MR-T2 and nearly 40% in the ADC modality for DSC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Weakly Supervised Segmentation (WSS) framework:
+-utilizes image-level labels (tags) to produce pixel-level segmentations 
+by leveraging self-supervision in multi-modal imaging scenarios
+-Backbone Network: a standard U-Net as the primary backbone
+-Siamese Structure: employs shared-weight Siamese structure 
+with 2 branches to impose self-equivariance
+(one branch processes the original image and 
+the other processes a spatially transformed version)
+-Multi-Branch Setup: multiple networks (K networks for K modalities)
+ to handle multiple modalities (T1, T2 MRI)
+-Global Average Pooling (GAP): integrated at the end of each model 
+to aggregate CAMs into prediction vectors for image classification
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model is trained using a global objective function with 4 distinct types of loss:
+-classification loss: 
+standard cross-entropy loss that uses image-level labels 
+to provide the initial supervisory signal
+-within-modality equivariance regularization: 
+this forces the model to produce consistent CAMs when 
+the input image undergoes spatial affine transformations
+-cross-modality equivariance regularization: 
+this is the primary contribution which imposes consistency 
+between the CAMs generated across different modalities 
+to ensure they identify the same regions
+-kullback–leibler (KL) divergence: 
+used to facilitate information exchange between the different networks 
+by matching their softmax likelihood distributions
++
+use a variable weighting coefficient (lambda E(t)) for the equivariance losses 
+to ensure stable training, it allows the classification loss to guide the model 
+in identifying initial object seeds before the equivariance 
+constraints gradually refine and expand those regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Modality Equivariant Constraints: based on 2 key observations:
+-Implicit Equivariance is Lost: 
+data augmentation implicitly teaches the model 
+that rotating an image should rotate the mask
+in fully supervised models
+while in WSS models using CAMs this property is lost 
+because the model only sees image-level tags
+-Cross-Modality Inconsistency: 
+standard CAMs generated for the same object across 
+different modalities (T1, T2) are often inconsistent despite representing the same anatomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-the model's primary strengths can only be fully realized 
+when multiple image modalities are available
+-the framework assumes that different modalities (T1 and T2 MRI) 
+are perfectly co-aligned because the model relies on pixel-wise correspondences 
+between these modalities and any misalignment would make 
+the equivariant constraints inapplicable
+-in some clinical scenarios (like PET-CT), a target might be clear in one modality 
+but nearly invisible in another which can make it difficult for the model 
+to generate reliable class activation maps (CAMs) for the low-visibility modality
+and leading to suboptimal joint results
+Notes:
+-assigning large weights to the equivariance constraints at the very beginning of training 
+reduced the quality of the CAMs, to fix it they used a variable weighting coefficient 
+that allows the classification loss to guide the model first 
+before the equivariance constraints gradually refine the object regions
+-they chose a standard U-Net and emphasize that their goal 
+was not to achieve a new state-of-the-art in general segmentation 
+but to demonstrate how their method narrows the performance gap 
+between weakly and fully supervised models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTs2019:
+https://www.med.upenn.edu/cbica/brats2019/data.html
+The preprocessed &amp; 3-fold cross-validation split of prostate DECATHALON:
+On github repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/gaurav104/WSS-CMER?tab=readme-ov-file</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diagnostic text-guided representation learning in hierarchical classification for pathological whole slide image</t>
   </si>
   <si>
@@ -1596,6 +1702,119 @@
 Diagnostic text</t>
   </si>
   <si>
+    <t xml:space="preserve">-in-house SYSFL: 
+private dataset of 1189 digital intraoperative cryosections 
+of lung tissue from the 
+First Affiliated Hospital of Sun Yat-sen University
+with 7 fine-grained categories related to lung lesions
+-Public PANDA: 
+prostate dataset containing 10618 H&amp;E-stained 
+biopsy WSIs and categorized into 6 levels 
+based on the ISUP grading system
+-Public BRACS: 
+breast cancer dataset consists of 547 H&amp;E-stained 
+WSIs collected from 189 patients 
+and categorized into 7 subtypes
+-used 5-fold cross-validation  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Planar Metrics (Fine-grained): 
+to evaluate the model's accuracy on specific disease subtypes
+included acc, AUC, F1-score
+-Hierarchical Metrics: 
+measured how well the model predicted labels 
+across multiple levels of granularity (from coarse to fine)
+hierarchical precision (H-Precision), 
+Hierarchical recall (H-Recall), 
+the hierarchical F1-score (H-F1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-SYSFL Dataset: acc 63.68%, AUC of 88.93%
+-PANDA Dataset: acc 62.35%, AUC of 88.26%
+-BRACS Dataset: acc 55.22%, AUC of 81.81%
+-H-F1 Scores: outperformed other models by ~ 2% 
+in H-F1 across the datasets 
+(80.69% on SYSFL, 74.22% on PANDA, 71.09% on BRACS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PathTree: 
+-multimodal representation learning framework 
+-designed to solve complex pathological classification tasks 
+by organizing them into a hierarchical binary tree structure
+-consists of 6 primary stages that integrate image data 
+with professional pathological text descriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-language-guided aggregation: 
+unlike standard models that use a simple linear layer for classification, 
+PathTree uses rich textual semantic information to guide how image 
+features are combined which improves the model's ability 
+to handle ambiguous category boundaries
+-hierarchical vs. planar: 
+while planar methods treat Cancer A and Cancer B as unrelated, 
+PathTree recognizes they may share a common parent category (Malignant)
+allowing the model to learn shared features at a coarse-grained level 
+before specializing in fine-grained differences
+-few-shot learning: 
+the model demonstrates strong few-shot capabilities
+by using text-slide similarity rather than fixed integer labels 
+as it can leverage the pre-existing semantic knowledge within the text encoders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-the of 6 primary stages:
+1-preprocessing and data pairing
+2-multimodal encoding: 
+image modality (pre-trained image encoder (PLIP) extracts 
+high-dimensional embeddings for each patch)
+And
+text modality (text encoder (PLIP) generates embeddings 
+for the category descriptions)
+3-multiple attention module:
+to generate multiple slide-level features
+(multi-gated attention and multi-head nystrom)
+4-text-guided tree-like aggregator: 
+text embeddings guide the fusion of slide features
+5-joint slide-text constraints: 
+to ensure the model respects the hierarchical structure using 
+path alignment loss and tree-aware matching loss
+6-slide prediction: 
+Obtaine final diagnostic scores by calculating the cosine similarity 
+between the global WSI feature and the fine-grained text prompt embeddings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations:
+-the model's performance is heavily dependent on the quality 
+and detail of the text annotations used to construct the hierarchical prompt embeddings
+So if diagnostic knowledge is incomplete or descriptions are poor 
+the model's semantic guidance may be limited
+-PathTree must be trained from scratch for every specific diagnostic task 
+which limits its scalability compared to more general foundation models
+-there is a lack of prior alignment between the patch encoder and 
+the textual embedding space 
+which may prevent the model from reaching its full potential
+-in datasets like BRACS where malignancy may only be present in very small areas, 
+the self-attention mechanisms (specifically the PathTree-Ny variant) 
+can struggle to focus on these tiny regions, 
+sometimes leading to less effective results compared to global context tasks
+-the current evaluation is restricted to three datasets
+Notes:
+-it has higher GPU memory consumption
+-it mimics the step-by-step judgment used by human pathologists, 
+moving from coarse-grained categories (non-cancerous vs cancerous) to fine-grained ones
+-SYSFL (lung tissue) dataset is private and cannot be shared due to lack of permission
+-PathTree captures semantically meaningful and diagnostically relevant regions, 
+such as glandular structures in invasive adenocarcinoma 
+or lymphocytic infiltrates in pneumonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANDA and BRACS are public
+SYSFL dataset is private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/WonderLandxD/PathTree
+Invalide url</t>
+  </si>
+  <si>
     <t xml:space="preserve">From CNNs to diffusion models: a decade of advances in brain tumor and stroke lesion segmentation across BraTS, ATLAS, and ISLES benchmarks </t>
   </si>
   <si>
@@ -1626,28 +1845,95 @@
 Deep learning</t>
   </si>
   <si>
-    <t xml:space="preserve">BiomedCLIP: a multimodal biomedical foundation model pretrained from 
-Fifteen million scientific image-text pairs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheng Zhang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yanbo Xu
-Naoto Usuyama
-Hanwen Xu
-Jaspreet Bagga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2303.00915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-03-02
-Last version (third)
-2025-01-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arXiv:2303.00915v3</t>
+    <t xml:space="preserve">1-BraTS
+2-ATLAS v2.0 (Anatomical Tracings of Lesions After Stroke)
+3-ISLES (Ischemic Stroke Lesion Segmentation)
+4-MSD (Medical Segmentation Decathlon)
+5-TCIA/UCSF-PDGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Region Overlap Metrics: 
+Dice Similarity Coefficient (DSC) 
+Jaccard Index (Intersection over Union, IoU)
+-Pixel-Level Metrics: 
+Sensitivity (Recall)
+Specificity
+Accuracy
+-Boundary-Based Metrics:
+Hausdorff Distance (HD95)
+Average Symmetric Surface Distance (ASSD)
+-Volumetric Metrics: 
+Volumetric Similarity (VS): 
+Lesion-wise F1 Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-on BraTS:
+BraTS 2018: Dice scores 0.883 (WT), 0.815 (TC), 0.766 (ET)
+BraTS 2020: Dice scores 0.889 (ET), 0.850 (WT), 0.820 (TC)
+BraTS 2023 (Adult Glioma): 
+Dice scores 0.900 (WT), 0.867 (TC), 0.851 (ET)
+-on ISLES (Ischemic Stroke Lesion Segmentation):
+RSLES 2022 Leaderboard: Dice score 0.96
+-on ATLAS v2.0 (Chronic Stroke Lesions):
+Dice score 0.718, Lesion-wise F1 0.724, Volume Difference 6162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-the study categorizes the dominant deep learning archs 
+into 6 major families:
+1-U-Net and its variants: includes the foundational 3D U-Net, 
+Residual U-Net, Attention U-Net, and U-Net++
+2-hybrid CNN-transformer models: 
+combine CNNs for local feature extraction with 
+transformers for global context 
+(TransBTS, Swin-Unet, UNETR, BiTr-UNet, DenseTrans)
+3-transformer only architectures: 
+like ViT-UNet and Swin Transformer Segmentation 
+that rely entirely on self-attention mechanisms
+4-ensemble and multi-branch frameworks: 
+aggregate predictions from multiple models to improve robustness
+5-diffusion-based generative models: 
+emerging approaches like MedSegDiff and MedSegDiff-V2 
+that treat segmentation as an iterative denoising process
+6-foundation models: recent adaptations of the SAM 
+for 3D medical volumetric data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-expert manual annotation is expensive, time-consuming and prone to inter-observer variability
+-most datasets suffer from a pronounced class imbalance 
+where the lesion or tumor occupies only a small fraction of the total brain volume
+which often leads to background-dominated optimization 
+where models struggle to identify small structures like the Enhancing Tumor (ET)
+-models trained on a specific dataset often fail when applied 
+to data from different scanners, institutions or patient populations 
+due to variations in imaging protocols and hardware
+-lesions frequently have low contrast, irregular shapes and overlapping intensity distributions 
+with surrounding healthy tissue which make precise delineation difficult
+-couldn't generalize on all types of brain tumor 
+-the enhancing tumor (ET) remains the most challenging region to segment 
+due to its small spatial footprint and irregular morphology
+-newer models like transformers and diffusion-based frameworks  
+demand more memory and processing power
+-diffusion models suffer from high inference times  due to their iterative sampling process
+Notes:
+-high Dice score does not always translate to clinical utility
+-single architectures rarely achieve top results alone
+-segmentation success is heavily influenced by the dataset's nature
+for example BraTS results are typically higher (~0.85+ Dice) 
+due to multi-modal high-contrast scans
+while ATLAS results are much lower (~0.70 Dice) 
+due to the fragmented nature of chronic stroke lesions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BraTS: 
+https://www.synapse.org/Synapse:syn64153130/wiki/631048.
+ISLES (2015–2022): 
+https://isles22.grand-challenge.org.
+ATLAS v2.0: 
+https://fcon_1000.projects.nitrc.org/indi/retro/atlas.html.
+MSD (Brain): 
+http://medicaldecathlon.com.
+TCIA/UCSF-PDGM: 
+https://www.cancerimagingarchive.net</t>
   </si>
   <si>
     <t xml:space="preserve">Learning Segmentation from Radiology
@@ -1784,7 +2070,7 @@
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1841,14 +2127,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1859,12 +2139,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF3465A4"/>
         <bgColor rgb="FF3366FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFAA95"/>
-        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -1902,7 +2176,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1963,88 +2237,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2095,7 +2293,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFFAA95"/>
+      <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -2299,7 +2497,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFC18"/>
+  <dimension ref="A1:XFC1048576"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.2"/>
@@ -2320,7 +2518,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="80.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="83.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="72.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="74.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="79.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="31.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="121.53"/>
@@ -2895,366 +3093,361 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" s="15" customFormat="true" ht="346.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
+    <row r="9" customFormat="false" ht="346.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="13" t="n">
         <v>45681</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L9" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="S9" s="16" t="s">
+      <c r="S9" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="T9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U9" s="15" t="s">
+      <c r="U9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="V9" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="W9" s="15" t="s">
+      <c r="W9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="XFC9" s="21"/>
     </row>
-    <row r="10" s="15" customFormat="true" ht="370.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
+    <row r="10" customFormat="false" ht="370.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="13" t="n">
         <v>45905</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="O10" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="P10" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="Q10" s="16" t="s">
+      <c r="Q10" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="S10" s="16" t="s">
+      <c r="S10" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U10" s="15" t="s">
+      <c r="U10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V10" s="22" t="s">
+      <c r="V10" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="W10" s="15" t="s">
+      <c r="W10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="XFC10" s="21"/>
     </row>
-    <row r="11" s="15" customFormat="true" ht="368.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
+    <row r="11" customFormat="false" ht="368.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="13" t="n">
         <v>45967</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="O11" s="24" t="s">
+      <c r="O11" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="P11" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="Q11" s="24" t="s">
+      <c r="Q11" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="R11" s="24" t="s">
+      <c r="R11" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="S11" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="T11" s="15" t="s">
+      <c r="T11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U11" s="15" t="s">
+      <c r="U11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V11" s="24" t="s">
+      <c r="V11" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="W11" s="15" t="s">
+      <c r="W11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="XFC11" s="21"/>
     </row>
-    <row r="12" s="15" customFormat="true" ht="380.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
+    <row r="12" customFormat="false" ht="380.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="13" t="n">
         <v>45975</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="O12" s="24" t="s">
+      <c r="O12" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="P12" s="16" t="s">
+      <c r="P12" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="Q12" s="24" t="s">
+      <c r="Q12" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="R12" s="24" t="s">
+      <c r="R12" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="S12" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="T12" s="15" t="s">
+      <c r="T12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="V12" s="24"/>
-      <c r="W12" s="15" t="s">
+      <c r="V12" s="11"/>
+      <c r="W12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="XFC12" s="21"/>
     </row>
-    <row r="13" s="25" customFormat="true" ht="364.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="n">
+    <row r="13" customFormat="false" ht="364.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="13" t="n">
         <v>45980</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="L13" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="M13" s="30" t="s">
+      <c r="M13" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="N13" s="26" t="s">
+      <c r="N13" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="O13" s="31" t="s">
+      <c r="O13" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="P13" s="26" t="s">
+      <c r="P13" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="Q13" s="31" t="s">
+      <c r="Q13" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="R13" s="31"/>
-      <c r="S13" s="26" t="s">
+      <c r="R13" s="11"/>
+      <c r="S13" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="T13" s="25" t="s">
+      <c r="T13" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="U13" s="25" t="s">
+      <c r="U13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V13" s="31" t="s">
+      <c r="V13" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="W13" s="25" t="s">
+      <c r="W13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X13" s="31" t="s">
+      <c r="X13" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="XFC13" s="32"/>
     </row>
-    <row r="14" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="316.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
@@ -3273,7 +3466,7 @@
       <c r="F14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="16" t="s">
         <v>223</v>
       </c>
       <c r="H14" s="13" t="n">
@@ -3291,22 +3484,55 @@
       <c r="L14" s="1" t="s">
         <v>226</v>
       </c>
+      <c r="M14" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="R14" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>233</v>
+      </c>
       <c r="T14" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="U14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
-    <row r="15" customFormat="false" ht="136.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="349.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -3314,8 +3540,8 @@
       <c r="F15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="33" t="s">
-        <v>230</v>
+      <c r="G15" s="16" t="s">
+        <v>239</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>45998</v>
@@ -3324,30 +3550,63 @@
         <v>105</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>226</v>
       </c>
+      <c r="M15" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="S15" s="14" t="s">
+        <v>248</v>
+      </c>
       <c r="T15" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="U15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="16" customFormat="false" ht="136.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="378.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0</v>
@@ -3355,137 +3614,128 @@
       <c r="F16" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G16" s="33" t="s">
-        <v>236</v>
+      <c r="G16" s="16" t="s">
+        <v>254</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>46058</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="J16" s="34" t="s">
-        <v>238</v>
+        <v>255</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>256</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>210</v>
       </c>
+      <c r="M16" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>262</v>
+      </c>
       <c r="T16" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X16" s="11"/>
     </row>
-    <row r="17" customFormat="false" ht="61.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="304.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>652</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>244</v>
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>45920</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>245</v>
+        <v>269</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="R17" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>279</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>41</v>
+        <v>62</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="304.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>45920</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="J18" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="N18" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="O18" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="P18" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="S18" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://arxiv.org/abs/2210.09698"/>
@@ -3500,14 +3750,16 @@
     <hyperlink ref="G9" r:id="rId10" display="https://doi.org/10.1016/j.compbiomed.2025.109703"/>
     <hyperlink ref="G10" r:id="rId11" display="https://doi.org/10.1016/j.compbiomed.2025.110928"/>
     <hyperlink ref="G11" r:id="rId12" display="https://doi.org/10.1016/j.compbiomed.2025.111265"/>
-    <hyperlink ref="V11" r:id="rId13" display="https://github.com/Luoxd1996/RAOS"/>
+    <hyperlink ref="V11" r:id="rId13" display="BraTS are public&#10;&#10;RAOS: ask authors&#10;+&#10;They provided this url but it doesn’t work&#10; https://github.com/Luoxd1996/RAOS "/>
     <hyperlink ref="G12" r:id="rId14" display="https://doi.org/10.1016/j.eswa.2025.130161"/>
     <hyperlink ref="G13" r:id="rId15" display="https://doi.org/10.1016/j.eswa.2025.130509"/>
     <hyperlink ref="G14" r:id="rId16" display="https://doi.org/10.1016/j.media.2022.102374"/>
-    <hyperlink ref="G15" r:id="rId17" display="https://doi.org/10.1016/j.media.2025.103894"/>
-    <hyperlink ref="G16" r:id="rId18" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
-    <hyperlink ref="G17" r:id="rId19" display="https://arxiv.org/abs/2303.00915"/>
-    <hyperlink ref="X18" r:id="rId20" display="https://github.com/MrGiovanni/R-Super"/>
+    <hyperlink ref="V14" r:id="rId17" display="BraTs2019:&#10;https://www.med.upenn.edu/cbica/brats2019/data.html&#10;&#10;The preprocessed &amp; 3-fold cross-validation split of prostate DECATHALON:&#10;On github repo"/>
+    <hyperlink ref="X14" r:id="rId18" display="https://github.com/gaurav104/WSS-CMER?tab=readme-ov-file"/>
+    <hyperlink ref="G15" r:id="rId19" display="https://doi.org/10.1016/j.media.2025.103894"/>
+    <hyperlink ref="X15" r:id="rId20" display="https://github.com/WonderLandxD/PathTree&#10;&#10;Invalide url"/>
+    <hyperlink ref="G16" r:id="rId21" display="https://doi.org/10.1016/j.bspc.2026.109780"/>
+    <hyperlink ref="X17" r:id="rId22" display="https://github.com/MrGiovanni/R-Super"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
